--- a/webapp/backend/samples/S1_integration_landscape.xlsx
+++ b/webapp/backend/samples/S1_integration_landscape.xlsx
@@ -9,8 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nodes" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Edges" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shape_Library" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Line_Rules" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -476,7 +474,6 @@
           <t>DOM0</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>group</t>
@@ -487,8 +484,6 @@
           <t>Sales Domain</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -516,7 +511,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,7 +538,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -572,7 +565,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -600,7 +592,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -628,7 +619,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -656,7 +646,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -684,7 +673,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -712,7 +700,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -740,7 +727,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -768,7 +754,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -796,7 +781,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -824,7 +808,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -852,7 +835,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -912,7 +894,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -940,7 +921,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -948,7 +928,6 @@
           <t>DOM1</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>group</t>
@@ -959,8 +938,6 @@
           <t>Finance Domain</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -988,7 +965,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1048,7 +1024,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1076,7 +1051,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1136,7 +1110,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1196,7 +1169,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1224,7 +1196,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1252,7 +1223,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1280,7 +1250,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1340,7 +1309,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1368,7 +1336,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1396,7 +1363,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1424,7 +1390,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1432,7 +1397,6 @@
           <t>DOM2</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>group</t>
@@ -1443,8 +1407,6 @@
           <t>Supply Chain Domain</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1472,7 +1434,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1500,7 +1461,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1528,7 +1488,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1556,7 +1515,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1584,7 +1542,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1612,7 +1569,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1640,7 +1596,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1668,7 +1623,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1696,7 +1650,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1724,7 +1677,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1784,7 +1736,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1812,7 +1763,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1840,7 +1790,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1868,7 +1817,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1908,7 +1856,6 @@
           <t>DOM3</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>group</t>
@@ -1919,8 +1866,6 @@
           <t>HR Domain</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1948,7 +1893,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1976,7 +1920,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2036,7 +1979,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2064,7 +2006,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2124,7 +2065,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2152,7 +2092,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2180,7 +2119,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2208,7 +2146,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2268,7 +2205,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2328,7 +2264,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2356,7 +2291,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2384,7 +2318,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2392,7 +2325,6 @@
           <t>DOM4</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
           <t>group</t>
@@ -2403,8 +2335,6 @@
           <t>Manufacturing Domain</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2432,7 +2362,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2460,7 +2389,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2552,7 +2480,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2580,7 +2507,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2608,7 +2534,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2636,7 +2561,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2664,7 +2588,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2756,7 +2679,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2784,7 +2706,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2812,7 +2733,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2840,7 +2760,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2868,7 +2787,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2876,7 +2794,6 @@
           <t>DOM5</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
           <t>group</t>
@@ -2887,8 +2804,6 @@
           <t>Customer Service Domain</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2916,7 +2831,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2944,7 +2858,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2972,7 +2885,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3032,7 +2944,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3060,7 +2971,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3088,7 +2998,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3148,7 +3057,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3176,7 +3084,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3204,7 +3111,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3328,7 +3234,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3356,7 +3261,6 @@
           <t>lifecycle=active</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3428,9 +3332,6 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3453,8 +3354,6 @@
           <t>file</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3472,9 +3371,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3497,8 +3393,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3516,9 +3410,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3536,9 +3427,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3561,8 +3449,6 @@
           <t>batch</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3580,9 +3466,6 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3600,9 +3483,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3625,8 +3505,6 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3644,9 +3522,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3664,9 +3539,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3689,8 +3561,6 @@
           <t>batch</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3708,9 +3578,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3728,9 +3595,6 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3753,8 +3617,6 @@
           <t>file</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3772,9 +3634,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3797,8 +3656,6 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3816,9 +3673,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3836,9 +3690,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3856,9 +3707,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3876,9 +3724,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3896,9 +3741,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3916,9 +3758,6 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3941,8 +3780,6 @@
           <t>batch</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3965,8 +3802,6 @@
           <t>batch</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3984,9 +3819,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4009,8 +3841,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4033,8 +3863,6 @@
           <t>batch</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4052,9 +3880,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4072,9 +3897,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4092,9 +3914,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4117,8 +3936,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4136,9 +3953,6 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4161,8 +3975,6 @@
           <t>file</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4180,9 +3992,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4200,9 +4009,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4225,8 +4031,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4249,8 +4053,6 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4268,9 +4070,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4288,9 +4087,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4313,8 +4109,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4337,8 +4131,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4356,9 +4148,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4376,9 +4165,6 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4396,9 +4182,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4416,9 +4199,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4436,9 +4216,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4461,8 +4238,6 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4480,9 +4255,6 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4505,8 +4277,6 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4524,9 +4294,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4544,9 +4311,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4564,9 +4328,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4584,9 +4345,6 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4604,9 +4362,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4624,9 +4379,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4649,8 +4401,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4673,8 +4423,6 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4692,9 +4440,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4717,8 +4462,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4736,9 +4479,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4761,8 +4501,6 @@
           <t>batch</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4780,9 +4518,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4800,9 +4535,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4820,9 +4552,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4840,9 +4569,6 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4860,9 +4586,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4885,8 +4608,6 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4909,8 +4630,6 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4928,9 +4647,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4948,9 +4664,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4968,9 +4681,6 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4988,9 +4698,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5013,8 +4720,6 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5032,9 +4737,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5057,8 +4759,6 @@
           <t>file</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5081,8 +4781,6 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5100,9 +4798,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5120,9 +4815,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5145,8 +4837,6 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5164,9 +4854,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5184,9 +4871,6 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5204,9 +4888,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5229,8 +4910,6 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5248,9 +4927,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5268,9 +4944,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5288,9 +4961,6 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5308,9 +4978,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5328,9 +4995,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5348,9 +5012,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5373,8 +5034,6 @@
           <t>file</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5392,9 +5051,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5412,9 +5068,6 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5432,9 +5085,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5457,8 +5107,6 @@
           <t>file</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5481,8 +5129,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5505,8 +5151,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5529,8 +5173,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5548,9 +5190,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5573,8 +5212,6 @@
           <t>file</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5592,9 +5229,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5617,8 +5251,6 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5641,8 +5273,6 @@
           <t>file</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5660,9 +5290,6 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5685,8 +5312,6 @@
           <t>file</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5709,8 +5334,6 @@
           <t>file</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5728,9 +5351,6 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5748,9 +5368,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5773,8 +5390,6 @@
           <t>file</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5792,9 +5407,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5812,9 +5424,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5832,9 +5441,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5852,9 +5458,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5872,9 +5475,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5897,8 +5497,6 @@
           <t>batch</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5916,9 +5514,6 @@
           <t>data_flow</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5936,4039 +5531,7 @@
           <t>flow</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L60"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>entity_type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>shape</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>decoration / icon</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>default_w</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>default_h</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>min_w</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>min_h</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>fill_hex</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>stroke_hex</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>auto_size</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>business_actor</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>rectangle</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>person icon, top-right</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>120</v>
-      </c>
-      <c r="F2" t="n">
-        <v>50</v>
-      </c>
-      <c r="G2" t="n">
-        <v>100</v>
-      </c>
-      <c r="H2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>#FFFFB5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>#B8B800</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>ArchiMate business layer = yellow</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>business_role</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>rectangle</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>cylinder-role icon, top-right</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>120</v>
-      </c>
-      <c r="F3" t="n">
-        <v>50</v>
-      </c>
-      <c r="G3" t="n">
-        <v>100</v>
-      </c>
-      <c r="H3" t="n">
-        <v>40</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>#FFFFB5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>#B8B800</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>business_process</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>rounded rectangle</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>arrow icon, top-right</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>140</v>
-      </c>
-      <c r="F4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H4" t="n">
-        <v>40</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>#FFFFB5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>#B8B800</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>business_service</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>rounded rectangle</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>service icon</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>140</v>
-      </c>
-      <c r="F5" t="n">
-        <v>50</v>
-      </c>
-      <c r="G5" t="n">
-        <v>100</v>
-      </c>
-      <c r="H5" t="n">
-        <v>40</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>#FFFFB5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>#B8B800</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>business_object</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>rectangle w/ title band</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>120</v>
-      </c>
-      <c r="F6" t="n">
-        <v>55</v>
-      </c>
-      <c r="G6" t="n">
-        <v>100</v>
-      </c>
-      <c r="H6" t="n">
-        <v>45</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>#FFFFB5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>#B8B800</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>business_event</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>rounded rectangle</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>arrow-tip icon</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>120</v>
-      </c>
-      <c r="F7" t="n">
-        <v>45</v>
-      </c>
-      <c r="G7" t="n">
-        <v>100</v>
-      </c>
-      <c r="H7" t="n">
-        <v>40</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>#FFFFB5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>#B8B800</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>capability</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>rectangle</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>rounded-square icon</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>160</v>
-      </c>
-      <c r="F8" t="n">
-        <v>60</v>
-      </c>
-      <c r="G8" t="n">
-        <v>120</v>
-      </c>
-      <c r="H8" t="n">
-        <v>50</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>#FFFFB5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>#B8B800</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Parents auto-grow to fit children (rule SZ-08)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>value_stream</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>chevron</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>160</v>
-      </c>
-      <c r="F9" t="n">
-        <v>55</v>
-      </c>
-      <c r="G9" t="n">
-        <v>120</v>
-      </c>
-      <c r="H9" t="n">
-        <v>45</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>#FFFFB5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>#B8B800</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Chevrons butt-joined left→right</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>goal</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>rounded rectangle</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>target icon</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>130</v>
-      </c>
-      <c r="F10" t="n">
-        <v>50</v>
-      </c>
-      <c r="G10" t="n">
-        <v>100</v>
-      </c>
-      <c r="H10" t="n">
-        <v>40</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>#E8D5E8</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>#9E6B9E</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Motivation layer = purple</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>outcome</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>rounded rectangle</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>outcome icon</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>130</v>
-      </c>
-      <c r="F11" t="n">
-        <v>50</v>
-      </c>
-      <c r="G11" t="n">
-        <v>100</v>
-      </c>
-      <c r="H11" t="n">
-        <v>40</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>#E8D5E8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>#9E6B9E</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>stakeholder</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>rounded rectangle</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>person icon</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>130</v>
-      </c>
-      <c r="F12" t="n">
-        <v>50</v>
-      </c>
-      <c r="G12" t="n">
-        <v>100</v>
-      </c>
-      <c r="H12" t="n">
-        <v>40</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>#E8D5E8</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>#9E6B9E</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>application_component</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>rectangle</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>component icon, top-right</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>150</v>
-      </c>
-      <c r="F13" t="n">
-        <v>55</v>
-      </c>
-      <c r="G13" t="n">
-        <v>110</v>
-      </c>
-      <c r="H13" t="n">
-        <v>45</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>#B5E3F7</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>#4A90B8</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Application layer = blue</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>application_service</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>rounded rectangle</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>service icon</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>150</v>
-      </c>
-      <c r="F14" t="n">
-        <v>50</v>
-      </c>
-      <c r="G14" t="n">
-        <v>110</v>
-      </c>
-      <c r="H14" t="n">
-        <v>40</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>#B5E3F7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>#4A90B8</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>application_interface</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>rectangle</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>lollipop icon</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>140</v>
-      </c>
-      <c r="F15" t="n">
-        <v>50</v>
-      </c>
-      <c r="G15" t="n">
-        <v>100</v>
-      </c>
-      <c r="H15" t="n">
-        <v>40</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>#B5E3F7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>#4A90B8</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>data_object</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>rectangle w/ title band</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>120</v>
-      </c>
-      <c r="F16" t="n">
-        <v>55</v>
-      </c>
-      <c r="G16" t="n">
-        <v>100</v>
-      </c>
-      <c r="H16" t="n">
-        <v>45</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>#B5E3F7</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>#4A90B8</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>node</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3D box</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>140</v>
-      </c>
-      <c r="F17" t="n">
-        <v>60</v>
-      </c>
-      <c r="G17" t="n">
-        <v>110</v>
-      </c>
-      <c r="H17" t="n">
-        <v>50</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>#C9E7C9</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>#5E9C5E</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Technology layer = green</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>device</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3D box, thick base</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>device icon</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>140</v>
-      </c>
-      <c r="F18" t="n">
-        <v>60</v>
-      </c>
-      <c r="G18" t="n">
-        <v>110</v>
-      </c>
-      <c r="H18" t="n">
-        <v>50</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>#C9E7C9</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>#5E9C5E</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>technology_service</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>rounded rectangle</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>service icon</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>150</v>
-      </c>
-      <c r="F19" t="n">
-        <v>50</v>
-      </c>
-      <c r="G19" t="n">
-        <v>110</v>
-      </c>
-      <c r="H19" t="n">
-        <v>40</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>#C9E7C9</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>#5E9C5E</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>artifact</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>rectangle</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>dog-ear corner</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>120</v>
-      </c>
-      <c r="F20" t="n">
-        <v>50</v>
-      </c>
-      <c r="G20" t="n">
-        <v>90</v>
-      </c>
-      <c r="H20" t="n">
-        <v>40</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>#C9E7C9</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>#5E9C5E</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>group</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>rectangle, dashed</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>label top-left</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>400</v>
-      </c>
-      <c r="F21" t="n">
-        <v>300</v>
-      </c>
-      <c r="G21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H21" t="n">
-        <v>150</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>#808080</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>container</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Generic container; size from children</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>start_end</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Flowchart</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>stadium (pill)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100</v>
-      </c>
-      <c r="F22" t="n">
-        <v>40</v>
-      </c>
-      <c r="G22" t="n">
-        <v>80</v>
-      </c>
-      <c r="H22" t="n">
-        <v>36</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>#D5E8D4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>#82B366</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Terminator</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Flowchart</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>rectangle</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>140</v>
-      </c>
-      <c r="F23" t="n">
-        <v>50</v>
-      </c>
-      <c r="G23" t="n">
-        <v>100</v>
-      </c>
-      <c r="H23" t="n">
-        <v>40</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>#DAE8FC</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>#6C8EBF</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>decision</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Flowchart</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>diamond</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>140</v>
-      </c>
-      <c r="F24" t="n">
-        <v>80</v>
-      </c>
-      <c r="G24" t="n">
-        <v>120</v>
-      </c>
-      <c r="H24" t="n">
-        <v>70</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>#FFE6CC</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>#D79B00</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Aspect ratio locked ~1.75:1 (rule SZ-06)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>data_io</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Flowchart</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>parallelogram</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>130</v>
-      </c>
-      <c r="F25" t="n">
-        <v>50</v>
-      </c>
-      <c r="G25" t="n">
-        <v>100</v>
-      </c>
-      <c r="H25" t="n">
-        <v>40</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>#F8CECC</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>#B85450</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Input/output</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>document</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Flowchart</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>rectangle, wavy bottom</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>120</v>
-      </c>
-      <c r="F26" t="n">
-        <v>60</v>
-      </c>
-      <c r="G26" t="n">
-        <v>100</v>
-      </c>
-      <c r="H26" t="n">
-        <v>50</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>#FFF2CC</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>#D6B656</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>database</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Flowchart</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>cylinder</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>90</v>
-      </c>
-      <c r="F27" t="n">
-        <v>60</v>
-      </c>
-      <c r="G27" t="n">
-        <v>70</v>
-      </c>
-      <c r="H27" t="n">
-        <v>50</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>#E1D5E7</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>#9673A6</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Also used in ER-02 / NW</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>subprocess</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Flowchart</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>rectangle, double side bars</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>150</v>
-      </c>
-      <c r="F28" t="n">
-        <v>50</v>
-      </c>
-      <c r="G28" t="n">
-        <v>110</v>
-      </c>
-      <c r="H28" t="n">
-        <v>40</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>#DAE8FC</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>#6C8EBF</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Links to another diagram_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Flowchart</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>circle</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>letter label</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>36</v>
-      </c>
-      <c r="F29" t="n">
-        <v>36</v>
-      </c>
-      <c r="G29" t="n">
-        <v>30</v>
-      </c>
-      <c r="H29" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>#666666</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Off-page connector; fixed size</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>lane</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Flowchart</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>rectangle w/ rotated title bar</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>900</v>
-      </c>
-      <c r="F30" t="n">
-        <v>160</v>
-      </c>
-      <c r="G30" t="n">
-        <v>400</v>
-      </c>
-      <c r="H30" t="n">
-        <v>120</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>#F5F5F5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>#666666</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>container</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Height = busiest lane (rule SZ-09)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>person_card</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>OrgChart</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>rounded rectangle, 2-line</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>photo circle, left</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>170</v>
-      </c>
-      <c r="F31" t="n">
-        <v>64</v>
-      </c>
-      <c r="G31" t="n">
-        <v>150</v>
-      </c>
-      <c r="H31" t="n">
-        <v>56</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>#4472C4</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Fixed size for grid alignment; name + title lines</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>department</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>OrgChart</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>rectangle</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>label top</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>400</v>
-      </c>
-      <c r="F32" t="n">
-        <v>300</v>
-      </c>
-      <c r="G32" t="n">
-        <v>200</v>
-      </c>
-      <c r="H32" t="n">
-        <v>120</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>#F2F7FF</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>#8FAADC</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>container</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>cloud</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Network</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>cloud</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>140</v>
-      </c>
-      <c r="F33" t="n">
-        <v>80</v>
-      </c>
-      <c r="G33" t="n">
-        <v>110</v>
-      </c>
-      <c r="H33" t="n">
-        <v>60</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>#F5F5F5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>#666666</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Internet / external</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>firewall</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Network</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>rectangle</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>brick-wall icon</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>110</v>
-      </c>
-      <c r="F34" t="n">
-        <v>60</v>
-      </c>
-      <c r="G34" t="n">
-        <v>90</v>
-      </c>
-      <c r="H34" t="n">
-        <v>50</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>#F8CECC</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>#B85450</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>router</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Network</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>circle w/ arrows icon</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>70</v>
-      </c>
-      <c r="F35" t="n">
-        <v>70</v>
-      </c>
-      <c r="G35" t="n">
-        <v>60</v>
-      </c>
-      <c r="H35" t="n">
-        <v>60</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>#DAE8FC</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>#6C8EBF</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>switch</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Network</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>rectangle</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>switch icon</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>100</v>
-      </c>
-      <c r="F36" t="n">
-        <v>50</v>
-      </c>
-      <c r="G36" t="n">
-        <v>80</v>
-      </c>
-      <c r="H36" t="n">
-        <v>40</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>#DAE8FC</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>#6C8EBF</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>load_balancer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Network</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>rectangle</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LB icon</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>110</v>
-      </c>
-      <c r="F37" t="n">
-        <v>55</v>
-      </c>
-      <c r="G37" t="n">
-        <v>90</v>
-      </c>
-      <c r="H37" t="n">
-        <v>45</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>#D5E8D4</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>#82B366</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>server</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Network</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>rectangle, rack style</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>server icon</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>120</v>
-      </c>
-      <c r="F38" t="n">
-        <v>60</v>
-      </c>
-      <c r="G38" t="n">
-        <v>100</v>
-      </c>
-      <c r="H38" t="n">
-        <v>50</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>#E1D5E7</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>#9673A6</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>zone</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Network</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>rectangle, dashed</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>label top-left</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>600</v>
-      </c>
-      <c r="F39" t="n">
-        <v>220</v>
-      </c>
-      <c r="G39" t="n">
-        <v>300</v>
-      </c>
-      <c r="H39" t="n">
-        <v>150</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>#FBFBFB</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>#999999</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>container</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>DMZ / Internal / etc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>entity</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>ERD</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>rectangle w/ title band + rows</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>PK/FK markers per row</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>180</v>
-      </c>
-      <c r="F40" t="n">
-        <v>30</v>
-      </c>
-      <c r="G40" t="n">
-        <v>160</v>
-      </c>
-      <c r="H40" t="n">
-        <v>30</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Height = 30 title + 22 × attribute_count (rule SZ-07)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>view</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>ERD</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>rectangle, dashed title band</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>180</v>
-      </c>
-      <c r="F41" t="n">
-        <v>30</v>
-      </c>
-      <c r="G41" t="n">
-        <v>160</v>
-      </c>
-      <c r="H41" t="n">
-        <v>30</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>#FAFAFA</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>#777777</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>battery</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>port block (title + pin rows)</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>pins both sides</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>180</v>
-      </c>
-      <c r="F42" t="n">
-        <v>30</v>
-      </c>
-      <c r="G42" t="n">
-        <v>160</v>
-      </c>
-      <c r="H42" t="n">
-        <v>30</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>#FFF2CC</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>#B45309</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>ports= in metadata</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>fuse_block</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>port block</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>pins</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>180</v>
-      </c>
-      <c r="F43" t="n">
-        <v>30</v>
-      </c>
-      <c r="G43" t="n">
-        <v>160</v>
-      </c>
-      <c r="H43" t="n">
-        <v>30</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>#F8CECC</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>#B85450</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>e_stop</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>port block</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>pins</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>180</v>
-      </c>
-      <c r="F44" t="n">
-        <v>30</v>
-      </c>
-      <c r="G44" t="n">
-        <v>160</v>
-      </c>
-      <c r="H44" t="n">
-        <v>30</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>#F8CECC</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>#CC0000</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>dcdc_converter</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>port block</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>pins</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>180</v>
-      </c>
-      <c r="F45" t="n">
-        <v>30</v>
-      </c>
-      <c r="G45" t="n">
-        <v>160</v>
-      </c>
-      <c r="H45" t="n">
-        <v>30</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>#FFF2CC</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>#D6B656</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>controller</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>port block</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>pins</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>180</v>
-      </c>
-      <c r="F46" t="n">
-        <v>30</v>
-      </c>
-      <c r="G46" t="n">
-        <v>160</v>
-      </c>
-      <c r="H46" t="n">
-        <v>30</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>#DAE8FC</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>#2B5797</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>ECU / PLC / flight computer</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>motor_driver</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>port block</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>pins</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>180</v>
-      </c>
-      <c r="F47" t="n">
-        <v>30</v>
-      </c>
-      <c r="G47" t="n">
-        <v>160</v>
-      </c>
-      <c r="H47" t="n">
-        <v>30</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>#E1D5E7</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>#7A5C99</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>motor</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>port block</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>pins</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>180</v>
-      </c>
-      <c r="F48" t="n">
-        <v>30</v>
-      </c>
-      <c r="G48" t="n">
-        <v>160</v>
-      </c>
-      <c r="H48" t="n">
-        <v>30</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>#E1D5E7</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>#9673A6</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Also actuators</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>sensor</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>port block</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>pins</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>180</v>
-      </c>
-      <c r="F49" t="n">
-        <v>30</v>
-      </c>
-      <c r="G49" t="n">
-        <v>160</v>
-      </c>
-      <c r="H49" t="n">
-        <v>30</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>#D5E8D4</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>#82B366</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>LiDAR, IMU, pitot, strain gauge…</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>eth_switch</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>port block</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>pins</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>180</v>
-      </c>
-      <c r="F50" t="n">
-        <v>30</v>
-      </c>
-      <c r="G50" t="n">
-        <v>160</v>
-      </c>
-      <c r="H50" t="n">
-        <v>30</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>#DAE8FC</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>#6C8EBF</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>junction</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>port block</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>pins</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>160</v>
-      </c>
-      <c r="F51" t="n">
-        <v>30</v>
-      </c>
-      <c r="G51" t="n">
-        <v>140</v>
-      </c>
-      <c r="H51" t="n">
-        <v>30</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>#FFFFFF</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>#666666</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Splice / connector block</t>
-        </is>
-      </c>
-    </row>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>relation_type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>line_style</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>width_px</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>source_end</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>target_end</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>routing</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>label_position</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>color_hex</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>semantics / when to use</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>composition</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>filled diamond</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Whole–part, part cannot exist alone (alt: nest via parent_id)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>aggregation</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>open diamond</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Whole–part, part can exist alone</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>assignment</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>filled ball</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>open arrow</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Actor/role/node performs or hosts the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>realization</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>dashed</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>hollow triangle</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Concrete element realizes an abstract one (app → service)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>serving</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>open arrow</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>midpoint</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Element provides functionality to another (was "used by")</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>access</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>dotted</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>open arrow</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Behavior reads/writes a data/business object</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>triggering</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>filled arrow</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Temporal order between behaviors/events</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>flow</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>dashed</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>filled arrow</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>midpoint</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Transfer of information/value between behaviors</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>association</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>midpoint</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Unspecified relation; default when unsure</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>specialization</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>EA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>hollow triangle</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>"is a kind of" (used heavily in metamodels)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>sequence_flow</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Flowchart</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>filled arrow</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>near source (yes/no)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Step order; label carries branch condition</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>message_flow</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Flowchart</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>dashed</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>open circle</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>open arrow</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>midpoint</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>#666666</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Communication across lanes/pools</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>reports_to</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>OrgChart</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>orthogonal (elbow)</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>#4472C4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Primary reporting line; drawn child-bottom to parent-top</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>dotted_reporting</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>OrgChart</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>dashed</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>orthogonal, routed outside</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>#999999</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Secondary / functional reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>physical_link</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Network</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>midpoint (VLAN/port)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Cable / physical connection</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>logical_link</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Network</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>dashed</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>midpoint</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>#6C8EBF</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Logical/overlay connectivity</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>vpn_tunnel</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Network</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>dash-dot</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>curved</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>midpoint</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>#9673A6</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Encrypted tunnel</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>one_to_many</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ERD</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>single tick (1)</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>crow's foot (N)</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>both ends</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>1:N; foot on the many side</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>one_to_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>ERD</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>single tick</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>single tick</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>both ends</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>1:1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>many_to_many</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ERD</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>crow's foot</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>crow's foot</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>both ends</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>#333333</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>M:N; renderer may suggest junction entity</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>data_flow</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ERD</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>filled arrow</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>midpoint (dataset name)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>#4472C4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Lineage: data moves source → target</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>power_wire</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>midpoint</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>#CC0000</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Positive supply (24V/12V/battery bus)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>ground_wire</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>midpoint</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>#111111</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Ground / return</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>signal_wire</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>open arrow</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>midpoint</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>#1A73E8</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Analog / GPIO / PWM</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>can_bus</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>dashed</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>2</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>midpoint</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>#2E7D32</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>CAN / RS-485 daisy chain</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>eth_cable</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Wiring</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>solid</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>orthogonal</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>midpoint</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>#F9AB00</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Ethernet / data link</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
